--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-media-endoscopy.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Media</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Media|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -370,7 +370,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|CarePlan)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -528,7 +528,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -599,7 +599,7 @@
     <t>高水準メディアカテゴリのコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -617,7 +617,7 @@
     <t>使用する場合、ImagingStudy同様”ES”を指定することが望ましい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -647,7 +647,7 @@
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-view</t>
+    <t>http://hl7.org/fhir/ValueSet/media-view|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticImage.subjectOrientationCode</t>
@@ -656,7 +656,7 @@
     <t>Media.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -685,7 +685,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -758,7 +758,7 @@
     <t>Media.operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -792,7 +792,7 @@
     <t>メディアの理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -813,7 +813,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -847,7 +847,7 @@
     <t>Media.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric|Device)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1274,7 +1274,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="55.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="63.390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1289,7 +1289,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.0390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.03125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-media-endoscopy.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Media|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Media</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -370,7 +370,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest|CarePlan)
 </t>
   </si>
   <si>
@@ -528,7 +528,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -599,7 +599,7 @@
     <t>高水準メディアカテゴリのコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type</t>
   </si>
   <si>
     <t>.code</t>
@@ -617,7 +617,7 @@
     <t>使用する場合、ImagingStudy同様”ES”を指定することが望ましい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -647,7 +647,7 @@
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-view|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/media-view</t>
   </si>
   <si>
     <t>DiagnosticImage.subjectOrientationCode</t>
@@ -656,7 +656,7 @@
     <t>Media.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -685,7 +685,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -758,7 +758,7 @@
     <t>Media.operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -792,7 +792,7 @@
     <t>メディアの理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -813,7 +813,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -847,7 +847,7 @@
     <t>Media.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric|Device)
 </t>
   </si>
   <si>
@@ -1274,7 +1274,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="63.390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="55.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1289,7 +1289,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.03125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.0390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
